--- a/data_extactor/batch_10_fa/batch_0097_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0097_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>سیستم‌های الکترونیکی مدیریت قطار ETMS | Microsoft Excel | Microsoft Word | نرم‌افزار نقشه برداری مسیر | نرم‌افزار ردیابی زمان</t>
+          <t>سیستم‌های الکترونیکی مدیریت قطار ETMS | Microsoft Excel | Microsoft Word | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار ردیابی زمان</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | مانیتورینگ | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حمل و نقل | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و تربیت | خدمات مشتریان و شخصی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید دور | توجه انتخابی | دقت کنترل | جهت‌گیری پاسخ | دید نزدیک | درک عمق | حساسیت به مسئله | زمان عکس‌العمل | سرعت ادراکی | هماهنگی چند عضو | درک شفاهی | بیان شفاهی | کنترل نرخ | توجه شنیداری | انعطاف‌پذیری بستار | سازماندهی اطلاعات | استدلال استقرایی | زبردستی دستی | تشخیص گفتار | حساسیت شنوایی | درک کتبی | استدلال قیاسی | اشتراک زمانی | وضوح گفتار | ثبات بازو-دست | جهت‌گیری فضایی | بیان کتبی | حساسیت به درخشندگی | تشخیص رنگ بصری | زبردستی انگشتان | تجسم فضایی</t>
+          <t>بینایی دور | توجه انتخابی | دقت کنترل | جهت‌گیری پاسخ | بینایی نزدیک | درک عمق | حساسیت به مسئله | زمان عکس‌العمل | سرعت ادراکی | هماهنگی چند عضو | درک شفاهی | بیان شفاهی | کنترل نرخ | توجه شنیداری | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | مهارت دستی | تشخیص گفتار | حساسیت شنوایی | درک کتبی | استدلال قیاسی | تقسیم توجه | وضوح گفتار | ثبات دست و بازو | جهت‌گیری فضایی | بیان کتبی | حساسیت به درخشندگی شدید | تشخیص رنگ بصری | مهارت انگشتان | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره به چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض ارتعاش کل بدن | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب | اهمیت تکرار وظایف یکسان</t>
+          <t>قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض ارتعاش کل بدن | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کنترل‌کننده‌های ترافیک هوایی | بازرسان هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون‌های صنعتی | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | توزیع‌کنندگان و دیسپچرهای برق | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و روسای ایستگاه راه‌آهن | مهندسان کشتی | تعمیرکاران سیگنال و سوزن ریل | مهندسان تاسیسات ثابت و اپراتورهای دیگ بخار | اپراتورهای مترو و تراموا | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها | تکنسین‌های ترافیک | بازرسان حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی</t>
+          <t>کنترلرهای ترافیک هوایی | بازرسان هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | توزیع‌کنندگان و دیسپچرهای برق | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | مهندسان کشتی | تعمیرکاران سیگنال و سوزن ریل | مهندسان تاسیسات و اپراتورهای دیگ بخار | رانندگان مترو و تراموا | بارگیران واگن مخزنی، کامیون و کشتی | تکنسین‌های ترافیک | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rail Yard Engineers, Dinkey Operators, and Hostlers</t>
+          <t>مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو (Rail Yard Engineers, Dinkey Operators, and Hostlers)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حمل و نقل | ایمنی و امنیت عمومی | مدیریت و امور اداری | مکانیک | زبان انگلیسی | خدمات مشتریان و شخصی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید دور | دقت کنترل | زمان عکس‌العمل | جهت‌گیری پاسخ | دید نزدیک | تشخیص رنگ بصری | بیان شفاهی | وضوح گفتار | توجه انتخابی | کنترل نرخ | زبردستی دستی | ثبات بازو-دست | استدلال قیاسی | هماهنگی چند عضو | درک عمق | تشخیص گفتار | توجه شنیداری | قدرت تنه | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | سازماندهی اطلاعات | اشتراک زمانی | جهت‌گیری فضایی | استدلال استقرایی | درک کتبی | زبردستی انگشتان | قدرت ایستا</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی دور | دقت کنترل | زمان عکس‌العمل | جهت‌گیری پاسخ | بینایی نزدیک | تشخیص رنگ بصری | بیان شفاهی | وضوح گفتار | توجه انتخابی | کنترل نرخ | مهارت دستی | ثبات دست و بازو | استدلال قیاسی | هماهنگی چند عضو | درک عمق | تشخیص گفتار | توجه شنیداری | قدرت تنه | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | تقسیم توجه | جهت‌گیری فضایی | استدلال استقرایی | درک کتبی | مهارت انگشتان | قدرت ایستا</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | بحث‌های چهره به چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد خطا | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن | داخل ساختمان، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای جرثقیل و برج | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون‌های صنعتی | کارگران و جابجا کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان لوکوموتیو | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | تعمیرکاران واگن قطار | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و روسای ایستگاه راه‌آهن | مهندسان کشتی | تعمیرکاران سیگنال و سوزن ریل | اپراتورهای مترو و تراموا | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی</t>
+          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای جرثقیل و تاور | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان لوکوموتیو | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | تعمیرکنندگان واگن‌های ریلی | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | مهندسان کشتی | تعمیرکاران سیگنال و سوزن ریل | رانندگان مترو و تراموا | بارگیران واگن مخزنی، کامیون و کشتی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Railroad Brake, Signal, and Switch Operators and Locomotive Firers</t>
+          <t>اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو (Railroad Brake, Signal, and Switch Operators and Locomotive Firers)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم مدیریت الکترونیکی قطار | سیستم‌های الکترونیکی مدیریت قطار ETMS | Google Android | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | نرم‌افزار نقشه برداری مسیر | نرم‌افزار ردیابی زمان</t>
+          <t>نرم‌افزار سیستم مدیریت الکترونیکی قطار | سیستم‌های الکترونیکی مدیریت قطار ETMS | Google Android | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار ردیابی زمان</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | ثبات بازو-دست | دید دور | درک شفاهی | زمان عکس‌العمل | سرعت ادراکی | حساسیت به مسئله | هماهنگی چند عضو | زبردستی دستی | تشخیص گفتار | کنترل نرخ | جهت‌گیری پاسخ | وضوح گفتار | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | توجه شنیداری | تشخیص رنگ بصری | انعطاف‌پذیری بستار | زبردستی انگشتان | اشتراک زمانی | توجه انتخابی | تجسم فضایی | حساسیت شنوایی | قدرت تنه</t>
+          <t>دقت کنترل | بینایی نزدیک | ثبات دست و بازو | بینایی دور | درک شفاهی | زمان عکس‌العمل | سرعت ادراکی | حساسیت به مسئله | هماهنگی چند عضو | مهارت دستی | تشخیص گفتار | کنترل نرخ | جهت‌گیری پاسخ | وضوح گفتار | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه شنیداری | تشخیص رنگ بصری | انعطاف‌پذیری بستار | مهارت انگشتان | تقسیم توجه | توجه انتخابی | تجسم | حساسیت شنوایی | قدرت تنه</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره به چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | فشار زمانی | فراوانی تصمیم‌گیری | قرار گرفتن در معرض ارتعاش کل بدن | مکالمات تلفنی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | فشار زمانی | فراوانی تصمیم‌گیری | قرار گرفتن در معرض ارتعاش کل بدن | مکالمات تلفنی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای نوار نقاله و متصدیان | اپراتورهای جرثقیل و برج | نصاب‌ها و تعمیرکاران خطوط انتقال نیروی برق | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون‌های صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان لوکوموتیو | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | تعمیرکاران واگن قطار | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | لوکوموتیورانان و روسای ایستگاه راه‌آهن | ملوانان و روغن‌کاران دریایی | مهندسان کشتی | تعمیرکاران سیگنال و سوزن ریل | اپراتورهای مترو و تراموا | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی</t>
+          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | نصابان و تعمیرکاران خطوط انتقال نیروی برق | رانندگان کامیون‌های سنگین و تریلی | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | مهندسان لوکوموتیو | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | تعمیرکنندگان واگن‌های ریلی | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | ملوانان و روغن‌کاران دریایی | مهندسان کشتی | تعمیرکاران سیگنال و سوزن ریل | رانندگان مترو و تراموا | بارگیران واگن مخزنی، کامیون و کشتی | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Railroad Conductors and Yardmasters</t>
+          <t>رئیس قطارها و مدیران محوطه راه‌آهن (Railroad Conductors and Yardmasters)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | مانیتورینگ | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | آموزش و تربیت | قانون و دولت</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | دید دور | تشخیص گفتار | وضوح گفتار | دید نزدیک | سازماندهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک کتبی | زمان عکس‌العمل | توجه شنیداری | دقت کنترل | توجه انتخابی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری مقوله | بیان کتبی | انعطاف‌پذیری بستار | درک عمق | اشتراک زمانی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | بینایی دور | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک کتبی | زمان عکس‌العمل | توجه شنیداری | دقت کنترل | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | انعطاف‌پذیری بستار | درک عمق | تقسیم توجه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و درون تیم‌ها | پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی | پیامد خطا | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی | پیامد خطا | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کنترل‌کننده‌های ترافیک هوایی | سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | رانندگان اتوبوس، ترانزیت و بین شهری | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان رده اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | سرپرستان رده اول مهمانداران مسافری | رانندگان کامیون‌های سنگین و تریلی | کارگران نگهداری بزرگراه | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | توزیع‌کنندگان و دیسپچرهای برق | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | تعمیرکاران سیگنال و سوزن ریل | اپراتورهای مترو و تراموا | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | بازرسان حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی</t>
+          <t>کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | رانندگان اتوبوس، ترانزیت و بین‌شهری | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مهمانداران مسافری | رانندگان کامیون‌های سنگین و تریلی | کارگران نگهداری بزرگراه‌ها | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | توزیع‌کنندگان و دیسپچرهای برق | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | تعمیرکاران سیگنال و سوزن ریل | رانندگان مترو و تراموا | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Subway and Streetcar Operators</t>
+          <t>رانندگان مترو و تراموا (Subway and Streetcar Operators)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | مانیتورینگ | درک مطلب | یادگیری فعال | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتریان و شخصی | زبان انگلیسی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | کنترل نرخ | دید نزدیک | دید دور | توجه شنیداری | حساسیت به مسئله | جهت‌گیری پاسخ | توجه انتخابی | ثبات بازو-دست | استدلال قیاسی | سرعت ادراکی | بیان شفاهی | زبردستی دستی | انعطاف‌پذیری بستار | درک عمق | درک شفاهی | وضوح گفتار | سازماندهی اطلاعات | اشتراک زمانی | انعطاف‌پذیری مقوله | استدلال استقرایی | درک کتبی | تشخیص رنگ بصری | زبردستی انگشتان | تشخیص گفتار | حساسیت شنوایی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | کنترل نرخ | بینایی نزدیک | بینایی دور | توجه شنیداری | حساسیت به مسئله | جهت‌گیری پاسخ | توجه انتخابی | ثبات دست و بازو | استدلال قیاسی | سرعت ادراکی | بیان شفاهی | مهارت دستی | انعطاف‌پذیری بستار | درک عمق | درک شفاهی | وضوح گفتار | ترتیب‌دهی اطلاعات | تقسیم توجه | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | درک کتبی | تشخیص رنگ بصری | مهارت انگشتان | تشخیص گفتار | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای نشستن | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | سرعت تعیین شده توسط سرعت تجهیزات | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | تعامل با مشتریان خارجی یا عموم مردم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای نشستن | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کنترل‌کننده‌های ترافیک هوایی | متخصصان عملیات فرودگاه | رانندگان اتوبوس، ترانزیت و بین شهری | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | خلبانان تجاری | ماموران عبور و پرچم‌داران | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | متصدیان پارکینگ | مهمانداران مسافری | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و روسای ایستگاه راه‌آهن | رانندگان شاتل و شوفرها | رانندگان تاکسی | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی</t>
+          <t>کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاه | رانندگان اتوبوس، ترانزیت و بین‌شهری | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | خلبانان تجاری | نگهبانان عبور و مرور و پرچم‌داران | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | مهندسان لوکوموتیو | متصدیان پارکینگ | متصدیان مسافران | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | رانندگان شاتل و شوفرها | رانندگان تاکسی | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rail Transportation Workers, All Other</t>
+          <t>کارکنان حمل‌ونقل ریلی، سایر موارد (Rail Transportation Workers, All Other)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات بازو-دست | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | دید نزدیک | دید دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | صرف زمان برای ایستادن | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارگران | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | بحث‌های چهره به چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | صرف زمان برای ایستادن | صرف زمان برای دویدن یا راه رفتن | قرار گرفتن در معرض تجهیزات خطرناک | پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | صرف زمان برای نشستن | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض آلاینده‌ها | پیامد خطا | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان لوکوموتیو | لوکوموتیورانان و روسای ایستگاه راه‌آهن | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | اپراتورهای مترو و تراموا | تعمیرکاران سیگنال و سوزن ریل | تعمیرکاران واگن قطار | اپراتورهای تجهیزات ریل‌گذاری و نگهداری ریل | پلیس ترانزیت و راه‌آهن | بازرسان حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | نمایندگان بار و محموله | اپراتورهای تراکتور و کامیون‌های صنعتی | اپراتورهای جرثقیل و برج | اپراتورهای نوار نقاله و متصدیان | سرپرستان رده اول کارگران حمل و نقل، سایر | مدیران حمل و نقل، انبارداری و توزیع | کارگران و جابجا کنندگان دستی بار، کالا و مواد | متصدیان پل و دریچه سد</t>
+          <t>مهندسان لوکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رانندگان مترو و تراموا | تعمیرکاران سیگنال و سوزن ریل | تعمیرکنندگان واگن‌های ریلی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | پلیس ترانزیت و راه‌آهن | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | نمایندگان بار و محموله | اپراتورهای تراکتور و کامیون صنعتی | اپراتورهای جرثقیل و تاور | اپراتورها و متصدیان نوار نقاله | سرپرستان خط اول کارگران حمل و نقل، سایر | مدیران حمل‌ونقل، انبارداری و توزیع | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | متصدیان پل و کانال</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sailors and Marine Oilers</t>
+          <t>ملوانان و روغن‌کاران دریایی (Sailors and Marine Oilers)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید دور | دقت کنترل | درک شفاهی | حساسیت به مسئله | سرعت ادراکی | درک عمق | توجه شنیداری | ثبات بازو-دست | هماهنگی چند عضو | زبردستی دستی | تشخیص رنگ بصری | توجه انتخابی | دید نزدیک | انعطاف‌پذیری بستار | حساسیت شنوایی | وضوح گفتار | تشخیص گفتار | تعادل کلی بدن | انعطاف‌پذیری گسترده | قدرت ایستا | زمان عکس‌العمل | تجسم فضایی | سازماندهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | استقامت | قدرت تنه | کنترل نرخ | زبردستی انگشتان | اشتراک زمانی | جهت‌گیری فضایی | انعطاف‌پذیری مقوله | درک کتبی | مکان‌یابی صدا | حساسیت به درخشندگی</t>
+          <t>بینایی دور | دقت کنترل | درک شفاهی | حساسیت به مسئله | سرعت ادراکی | درک عمق | توجه شنیداری | ثبات دست و بازو | هماهنگی چند عضو | مهارت دستی | تشخیص رنگ بصری | توجه انتخابی | بینایی نزدیک | انعطاف‌پذیری بستار | حساسیت شنوایی | وضوح گفتار | تشخیص گفتار | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | زمان عکس‌العمل | تجسم | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | استقامت | قدرت تنه | کنترل نرخ | مهارت انگشتان | تقسیم توجه | جهت‌گیری فضایی | انعطاف‌پذیری دسته‌بندی | درک کتبی | مکان‌یابی صدا | حساسیت به درخشندگی شدید</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | بحث‌های چهره به چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای ایستادن | پیامدهای کاری و نتایج سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای خم شدن یا پیچاندن بدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | نزدیکی فیزیکی | صرف زمان برای دویدن یا راه رفتن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای ایستادن | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | کاپیتان‌ها، افسران و خلبانان شناورهای دریایی | غواصان تجاری | اپراتورهای جرثقیل و برج | اپراتورهای لایروب | کارگران صید و شکار | کارگران کمکی--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون‌های صنعتی | کارگران نگهداری، ماشین‌آلات | مهندسان دریا و معماران دریایی | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | اپراتورهای قایق‌های موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | دکل‌بندها | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده، نفت و گاز | مهندسان کشتی | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها</t>
+          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | غواصان تجاری | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | کارگران ماهیگیری و شکار | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان دریایی و معماران کشتی | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | اپراتورهای قایق موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | مهندسان کشتی | بارگیران واگن مخزنی، کامیون و کشتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Captains, Mates, and Pilots of Water Vessels</t>
+          <t>ناخدایان، افسران دوم و راهنمایان شناورهای دریایی (Captains, Mates, and Pilots of Water Vessels)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apple macOS | Autodesk Revit | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار نقشه ناوبری FURUNO | سیستم مدل‌سازی آب‌های زیرزمینی GMS | نرم‌افزار ناوبری JRC | Jeppesen Marine Nobeltec Admiral | KNMI TurboWin | نرم‌افزار دفترچه ثبت | Maptech The CAPN | Microsoft Excel | Microsoft Office Outlook | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار نقشه ناوبری | SHIPNEXT</t>
+          <t>Apple macOS | Autodesk Revit | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار نقشه ناوبری FURUNO | Groundwater modeling system GMS | نرم‌افزار ناوبری JRC | Jeppesen Marine Nobeltec Admiral | KNMI TurboWin | نرم‌افزار دفترچه ثبت | Maptech The CAPN | Microsoft Excel | Microsoft Office Outlook | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار نقشه ناوبری | SHIPNEXT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | قانون و دولت | زبان انگلیسی | جغرافیا | مدیریت و امور اداری | خدمات مشتریان و شخصی | آموزش و تربیت</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | قانون و دولت | زبان انگلیسی | جغرافیا | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | جهت‌گیری فضایی | دید دور | وضوح گفتار | دید نزدیک | درک کتبی | دقت کنترل | ثبات بازو-دست | تشخیص گفتار | سازماندهی اطلاعات | استدلال استقرایی | سرعت ادراکی | انعطاف‌پذیری بستار | بیان کتبی | درک عمق | زبردستی دستی | توجه انتخابی | اشتراک زمانی | هماهنگی چند عضو | کنترل نرخ | زمان عکس‌العمل | حساسیت به درخشندگی | انعطاف‌پذیری مقوله | تجسم فضایی | توجه شنیداری | تعادل کلی بدن | قدرت تنه | جهت‌گیری پاسخ | زبردستی انگشتان | سرعت بستار | تشخیص رنگ بصری | انعطاف‌پذیری گسترده</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | جهت‌گیری فضایی | بینایی دور | وضوح گفتار | بینایی نزدیک | درک کتبی | دقت کنترل | ثبات دست و بازو | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال استقرایی | سرعت ادراکی | انعطاف‌پذیری بستار | بیان کتبی | درک عمق | مهارت دستی | توجه انتخابی | تقسیم توجه | هماهنگی چند عضو | کنترل نرخ | زمان عکس‌العمل | حساسیت به درخشندگی شدید | انعطاف‌پذیری دسته‌بندی | تجسم | توجه شنیداری | تعادل کلی بدن | قدرت تنه | جهت‌گیری پاسخ | مهارت انگشتان | سرعت بستار | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های چهره به چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامد خطا | در یک وسیله نقلیه بسته یا کار با تجهیزات بسته | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | داخل ساختمان، بدون کنترل شرایط محیطی | ایمیل | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامد خطا | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | محیط داخلی، بدون کنترل شرایط محیطی | ایمیل | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | متصدیان پل و دریچه سد | غواصان تجاری | خلبانان تجاری | اپراتورهای لایروب | کارگران صید و شکار | اپراتورهای بالابر و وینچ | مهندسان لوکوموتیو | مهندسان دریا و معماران دریایی | اپراتورهای قایق‌های موتوری | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و روسای ایستگاه راه‌آهن | دکل‌بندها | ملوانان و روغن‌کاران دریایی | مهندسان کشتی | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها | بازرسان حمل و نقل</t>
+          <t>سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | متصدیان پل و کانال | غواصان تجاری | خلبانان تجاری | اپراتورهای لایروب | کارگران ماهیگیری و شکار | اپراتورهای بالابر و وینچ | مهندسان لوکوموتیو | مهندسان دریایی و معماران کشتی | اپراتورهای قایق موتوری | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | ریگرها | ملوانان و روغن‌کاران دریایی | مهندسان کشتی | بارگیران واگن مخزنی، کامیون و کشتی | بازرسان حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Motorboat Operators</t>
+          <t>اپراتورهای قایق موتوری (Motorboat Operators)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار خلبان خودکار | نرم‌افزار نقشه‌برداری | نرم‌افزار اکو سوند | نرم‌افزار سیستم موقعیت‌یابی جهانی GPS | نرم‌افزار رادار | Roam Devices Roam Marine Monitor Hub | SEA.AI Offshore ONE | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار خلبان خودکار | نرم‌افزار نقشه‌کشی | نرم‌افزار اکو سوند | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | نرم‌افزار رادار | Roam Devices Roam Marine Monitor Hub | SEA.AI Offshore ONE | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | مانیتورینگ | گوش دادن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | آموزش و تربیت | ایمنی و امنیت عمومی | حمل و نقل | مکانیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | حمل و نقل | مکانیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دقت کنترل | جهت‌گیری فضایی | دید دور | حساسیت به مسئله | سرعت ادراکی | ثبات بازو-دست | زبردستی دستی | وضوح گفتار | توجه شنیداری | بیان شفاهی | هماهنگی چند عضو | استدلال قیاسی | توجه انتخابی | جهت‌گیری پاسخ | زمان عکس‌العمل | دید نزدیک | درک عمق | اشتراک زمانی | تشخیص گفتار | حساسیت به درخشندگی | کنترل نرخ | زبردستی انگشتان | انعطاف‌پذیری بستار | درک شفاهی | تجسم فضایی | سازماندهی اطلاعات | استدلال استقرایی | حساسیت شنوایی | دید محیطی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا</t>
+          <t>دقت کنترل | جهت‌گیری فضایی | بینایی دور | حساسیت به مسئله | سرعت ادراکی | ثبات دست و بازو | مهارت دستی | وضوح گفتار | توجه شنیداری | بیان شفاهی | هماهنگی چند عضو | استدلال قیاسی | توجه انتخابی | جهت‌گیری پاسخ | زمان عکس‌العمل | بینایی نزدیک | درک عمق | تقسیم توجه | تشخیص گفتار | حساسیت به درخشندگی شدید | کنترل نرخ | مهارت انگشتان | انعطاف‌پذیری بستار | درک شفاهی | تجسم | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت شنوایی | بینایی محیطی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | بحث‌های چهره به چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | ارتباط با دیگران | فضای باز, در معرض تمام شرایط آب و هوایی | فشار زمانی | پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامدهای کاری و نتایج سایر کارگران | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض آلاینده‌ها | در یک وسیله نقلیه روباز یا کار با تجهیزات | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض آلاینده‌ها | در یک وسیله نقلیه روباز یا کار با تجهیزات | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | متصدیان پل و دریچه سد | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | کاپیتان‌ها، افسران و خلبانان شناورهای دریایی | خلبانان تجاری | اپراتورهای لایروب | کارگران صید و شکار | رانندگان کامیون‌های سنگین و تریلی | کارگران نگهداری بزرگراه | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون‌های صنعتی | مهندسان لوکوموتیو | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | دکل‌بندها | ملوانان و روغن‌کاران دریایی | مهندسان کشتی | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها | بازرسان حمل و نقل</t>
+          <t>سرپرستان جابجایی بار هواپیما | متصدیان پل و کانال | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | خلبانان تجاری | اپراتورهای لایروب | کارگران ماهیگیری و شکار | رانندگان کامیون‌های سنگین و تریلی | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | مهندسان لوکوموتیو | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | ریگرها | ملوانان و روغن‌کاران دریایی | مهندسان کشتی | بارگیران واگن مخزنی، کامیون و کشتی | بازرسان حمل‌ونقل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ship Engineers</t>
+          <t>مهندسان کشتی (Ship Engineers)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apple macOS | نرم‌افزار اعزام به کمک کامپیوتر | سیستم مدیریت نگهداری کامپیوتری CMMS | Damen DAMOS | نرم‌افزار تبادل الکترونیکی داده‌ها EDI | دفاتر ثبت الکترونیکی Kongsberg Maritime K-LOG | Marine Software Marine Planned Maintenance | Marine Software Marine Safety Manager | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Database | نرم‌افزار SAP | نرم‌افزار Salesforce | نرم‌افزار Wonderware</t>
+          <t>Apple macOS | نرم‌افزار اعزام به کمک کامپیوتر | سیستم مدیریت نگهداری کامپیوتری CMMS | Damen DAMOS | نرم‌افزار تبادل الکترونیکی داده EDI | دفاتر ثبت الکترونیکی Kongsberg Maritime K-LOG | Marine Software Marine Planned Maintenance | Marine Software Marine Safety Manager | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Database | نرم‌افزار SAP | نرم‌افزار Salesforce | نرم‌افزار Wonderware</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | مانیتورینگ | سخن گفتن | یادگیری فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | مهندسی و فناوری | ایمنی و امنیت عمومی | حمل و نقل | ریاضیات | کامپیوتر و الکترونیک</t>
+          <t>مکانیک | زبان انگلیسی | مهندسی و فناوری | ایمنی و امنیت عمومی | حمل و نقل | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | دقت کنترل | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | سازماندهی اطلاعات | توجه شنیداری | حساسیت شنوایی | زمان عکس‌العمل | هماهنگی چند عضو | زبردستی انگشتان | زبردستی دستی | ثبات بازو-دست | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | انعطاف‌پذیری مقوله | بیان کتبی | سرعت ادراکی | ابتکار | روان بودن ایده‌ها | جهت‌گیری پاسخ | اشتراک زمانی | دید دور | انعطاف‌پذیری گسترده | قدرت تنه | قدرت ایستا | کنترل نرخ</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | دقت کنترل | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه شنیداری | حساسیت شنوایی | زمان عکس‌العمل | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | سرعت ادراکی | اصالت | روانی ایده‌ها | جهت‌گیری پاسخ | تقسیم توجه | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | کنترل نرخ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پوشیدن تجهیزات محافظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره به چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | داخل ساختمان، بدون کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض شرایط خطرناک | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | فشار زمانی | نزدیکی فیزیکی | فضای باز، زیر سقف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب</t>
+          <t>سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | محیط داخلی، بدون کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض شرایط خطرناک | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | فشار زمانی | نزدیکی فیزیکی | فضای باز، زیر سقف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کمک‌کارشناسان مهندسی هوافضا و عملیات | تکنسین‌های خدمات و مکانیک‌های هواپیما | مونتاژکنندگان ساختار، سطوح، دکل‌بندی و سیستم‌های هواپیما | تکنسین‌های هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌های نیروگاه برق‌آبی | مهندسان لوکوموتیو | کارگران نگهداری و تعمیرات، عمومی | مهندسان دریا و معماران دریایی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و گیج‌زن‌ها | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه | ملوانان و روغن‌کاران دریایی | مهندسان تاسیسات ثابت و اپراتورهای دیگ بخار | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی | پمپ‌زن‌های سر چاه</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های هوانوردی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌های نیروگاه برق‌آبی | مهندسان لوکوموتیو | کارگران نگهداری و تعمیرات عمومی | مهندسان دریایی و معماران کشتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | ملوانان و روغن‌کاران دریایی | مهندسان تاسیسات و اپراتورهای دیگ بخار | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0097_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0097_fa.xlsx
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Electronic train management systems ETMS | نرم‌افزار نقشه‌برداری مسیر | Microsoft Excel | Microsoft Word | نرم‌افزار ثبت و ردیابی زمان</t>
+          <t>Electronic train management systems ETMS | نرم‌افزار نقشه‌برداری مسیر | Microsoft Excel | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار ثبت و ردیابی زمان</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید دور | توجه انتخابی | دقت کنترل | جهت‌گیری پاسخ | دید نزدیک | ادراک عمق | حساسیت به مسئله | زمان واکنش | سرعت ادراک | هماهنگی چنداندامی | درک شفاهی | بیان شفاهی | کنترل نرخ حرکتی | توجه شنیداری | انعطاف‌پذیری بستار | مرتب‌سازی اطلاعات | استدلال استقرایی | چابکی دستی | تشخیص گفتار | حساسیت شنوایی | درک کتبی | استدلال قیاسی | تقسیم توجه | وضوح گفتار | ثبات دست و بازو | جهت‌یابی فضایی | بیان کتبی | حساسیت به درخشش نور | تشخیص رنگ بصری | چابکی انگشتان | تجسم فضایی</t>
+          <t>بینایی دور | توجه انتخابی | دقت کنترل | جهت‌گیری پاسخ | بینایی نزدیک | درک عمق | حساسیت به مسئله | زمان عکس‌العمل | سرعت ادراکی | هماهنگی چند عضو | درک شفاهی | بیان شفاهی | کنترل نرخ | توجه شنیداری | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | مهارت دستی | تشخیص گفتار | حساسیت شنوایی | درک کتبی | استدلال قیاسی | تقسیم توجه | وضوح گفتار | ثبات دست و بازو | جهت‌گیری فضایی | بیان کتبی | حساسیت به درخشندگی شدید | تشخیص رنگ بصری | مهارت انگشتان | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | بازرسان هوانوردی | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | رانندگان تریلر و کامیون‌های سنگین | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و لیفتراک‌های صنعتی | مهندسان بهره‌برداری و اپراتورهای سایر ماشین‌آلات ساختمانی | توزیع‌کنندگان و دیسپچرهای شبکه برق | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | مهندسان فنی کشتی | تعمیرکاران سیستم‌های علائم و سوزن‌های خطوط راه‌آهن | مهندسان تأسیسات و اپراتورهای دیگ بخار | رانندگان مترو و تراموا | متصدیان بارگیری مخزن‌دار ریلی، کامیونی و کشتی | تکنسین‌های ترافیک | بازرسان حمل‌ونقل | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری به‌استثنای هوانوردی</t>
+          <t>کنترلرهای ترافیک هوایی | بازرسان هوانوردی و فرودگاهی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | متصدیان دیسپاچ و اعزام | رانندگان خودروهای سنگین و کشنده‌ها | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | دیسپچرها و توزیع‌کنندگان شبکه برق | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | مهندسان فنی کشتی | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | رانندگان مترو و تراموا | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | تکنسین‌های ترافیک | بازرسان ترابری و حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مدیریت و امور اداری | مکانیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید دور | دقت کنترل | زمان واکنش | جهت‌گیری پاسخ | دید نزدیک | تشخیص رنگ بصری | بیان شفاهی | وضوح گفتار | توجه انتخابی | کنترل نرخ حرکتی | چابکی دستی | ثبات دست و بازو | استدلال قیاسی | هماهنگی چنداندامی | ادراک عمق | تشخیص گفتار | توجه شنیداری | استحکام تنه | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری بستار | مرتب‌سازی اطلاعات | تقسیم توجه | جهت‌یابی فضایی | استدلال استقرایی | درک کتبی | چابکی انگشتان | قدرت ایستا</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی دور | دقت کنترل | زمان عکس‌العمل | جهت‌گیری پاسخ | بینایی نزدیک | تشخیص رنگ بصری | بیان شفاهی | وضوح گفتار | توجه انتخابی | کنترل نرخ | مهارت دستی | ثبات دست و بازو | استدلال قیاسی | هماهنگی چند عضو | درک عمق | تشخیص گفتار | توجه شنیداری | قدرت تنه | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | تقسیم توجه | جهت‌گیری فضایی | استدلال استقرایی | درک کتبی | مهارت انگشتان | قدرت ایستا</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | اپراتورهای جرثقیل و تاورکرین | متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | رانندگان تریلر و کامیون‌های سنگین | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و لیفتراک‌های صنعتی | کارگران جابه‌جایی دستی بار، کالا و کارهای عمومی | اپراتورهای ماشین‌آلات بارگیری و باربری در معادن زیرزمینی | لکوموتیورانان | مکانیک‌های ماشین‌آلات سنگین متحرک به‌استثنای موتور | مهندسان بهره‌برداری و اپراتورهای سایر ماشین‌آلات ساختمانی | تعمیرکاران واگن‌های ریلی | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | مهندسان فنی کشتی | تعمیرکاران سیستم‌های علائم و سوزن‌های خطوط راه‌آهن | رانندگان مترو و تراموا | متصدیان بارگیری مخزن‌دار ریلی، کامیونی و کشتی | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری به‌استثنای هوانوردی</t>
+          <t>مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتورهای جرثقیل و تاورکرین | متصدیان دیسپاچ و اعزام | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | رانندگان خودروهای سنگین و کشنده‌ها | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | لکوموتیورانان | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | تعمیرکار واگن قطار | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | مهندسان فنی کشتی | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | رانندگان مترو و تراموا | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | ثبات دست و بازو | دید دور | درک شفاهی | زمان واکنش | سرعت ادراک | حساسیت به مسئله | هماهنگی چنداندامی | چابکی دستی | تشخیص گفتار | کنترل نرخ حرکتی | جهت‌گیری پاسخ | وضوح گفتار | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | توجه شنیداری | تشخیص رنگ بصری | انعطاف‌پذیری بستار | چابکی انگشتان | تقسیم توجه | توجه انتخابی | تجسم فضایی | حساسیت شنوایی | استحکام تنه</t>
+          <t>دقت کنترل | بینایی نزدیک | ثبات دست و بازو | بینایی دور | درک شفاهی | زمان عکس‌العمل | سرعت ادراکی | حساسیت به مسئله | هماهنگی چند عضو | مهارت دستی | تشخیص گفتار | کنترل نرخ | جهت‌گیری پاسخ | وضوح گفتار | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه شنیداری | تشخیص رنگ بصری | انعطاف‌پذیری بستار | مهارت انگشتان | تقسیم توجه | توجه انتخابی | تجسم | حساسیت شنوایی | قدرت تنه</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | اپراتورها و متصدیان نقاله‌ها | اپراتورهای جرثقیل و تاورکرین | نصابان و تعمیرکاران خطوط انتقال برق | رانندگان تریلر و کامیون‌های سنگین | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و لیفتراک‌های صنعتی | اپراتورهای ماشین‌آلات بارگیری و باربری در معادن زیرزمینی | لکوموتیورانان | مکانیک‌های ماشین‌آلات سنگین متحرک به‌استثنای موتور | مهندسان بهره‌برداری و اپراتورهای سایر ماشین‌آلات ساختمانی | تعمیرکاران واگن‌های ریلی | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | رؤسای قطار و مدیران محوطه راه‌آهن | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | تعمیرکاران سیستم‌های علائم و سوزن‌های خطوط راه‌آهن | رانندگان مترو و تراموا | متصدیان بارگیری مخزن‌دار ریلی، کامیونی و کشتی | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری به‌استثنای هوانوردی</t>
+          <t>مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | رانندگان خودروهای سنگین و کشنده‌ها | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | لکوموتیورانان | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | تعمیرکار واگن قطار | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | رؤسای قطار و مدیران محوطه راه‌آهن | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | رانندگان مترو و تراموا | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل‌ونقل | زبان انگلیسی | آموزش و تدریس | امور حقوقی و دولتی</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | دید دور | تشخیص گفتار | وضوح گفتار | دید نزدیک | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک کتبی | زمان واکنش | توجه شنیداری | دقت کنترل | توجه انتخابی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری دسته‌بندی | بیان کتبی | انعطاف‌پذیری بستار | ادراک عمق | تقسیم توجه</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | بینایی دور | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | درک کتبی | زمان عکس‌العمل | توجه شنیداری | دقت کنترل | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | انعطاف‌پذیری بستار | درک عمق | تقسیم توجه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | سرپرستان جابه‌جایی بار هوایی | متخصصان عملیات فرودگاهی | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل جابه‌جایی بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | رانندگان تریلر و کامیون‌های سنگین | کارگران نگهداری و راهداری جاده‌ها | رانندگان خودروهای باری سبک | لکوموتیورانان | توزیع‌کنندگان و دیسپچرهای شبکه برق | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | تعمیرکاران سیستم‌های علائم و سوزن‌های خطوط راه‌آهن | رانندگان مترو و تراموا | تکنسین‌های ترافیک | پلیس راه‌آهن و ناوگان حمل‌ونقل عمومی | بازرسان حمل‌ونقل | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری به‌استثنای هوانوردی</t>
+          <t>کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارشناسان عملیات فرودگاهی | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | رانندگان خودروهای سنگین و کشنده‌ها | کارگران راهداری و نگهداری جاده‌ها | رانندگان خودروهای باربری سبک و وانت‌بارها | لکوموتیورانان | دیسپچرها و توزیع‌کنندگان شبکه برق | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | رانندگان مترو و تراموا | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | بازرسان ترابری و حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چنداندامی | زمان واکنش | کنترل نرخ حرکتی | دید نزدیک | دید دور | توجه شنیداری | حساسیت به مسئله | جهت‌گیری پاسخ | توجه انتخابی | ثبات دست و بازو | استدلال قیاسی | سرعت ادراک | بیان شفاهی | چابکی دستی | انعطاف‌پذیری بستار | ادراک عمق | درک شفاهی | وضوح گفتار | مرتب‌سازی اطلاعات | تقسیم توجه | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | درک کتبی | تشخیص رنگ بصری | چابکی انگشتان | تشخیص گفتار | حساسیت شنوایی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | کنترل نرخ | بینایی نزدیک | بینایی دور | توجه شنیداری | حساسیت به مسئله | جهت‌گیری پاسخ | توجه انتخابی | ثبات دست و بازو | استدلال قیاسی | سرعت ادراکی | بیان شفاهی | مهارت دستی | انعطاف‌پذیری بستار | درک عمق | درک شفاهی | وضوح گفتار | ترتیب‌دهی اطلاعات | تقسیم توجه | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | درک کتبی | تشخیص رنگ بصری | مهارت انگشتان | تشخیص گفتار | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | متخصصان عملیات فرودگاهی | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | خلبانان تجاری | مأموران هدایت ترافیک و پرچم‌داران | متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | رانندگان تریلر و کامیون‌های سنگین | رانندگان خودروهای باری سبک | لکوموتیورانان | متصدیان پارکینگ | مهمانداران و پرسنل خدماتی مسافران | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | رانندگان سرویس و تشریفات | رانندگان تاکسی | تکنسین‌های ترافیک | پلیس راه‌آهن و ناوگان حمل‌ونقل عمومی | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری به‌استثنای هوانوردی</t>
+          <t>کنترلرهای ترافیک هوایی | کارشناسان عملیات فرودگاهی | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | خلبانان تجاری | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | متصدیان دیسپاچ و اعزام | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان خودروهای باربری سبک و وانت‌بارها | لکوموتیورانان | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | رانندگان خودروهای سرویس و تشریفات | رانندگان تاکسی | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | مخابرات | جغرافیا | ریاضیات</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | مخابرات | جغرافیا | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چنداندامی | دقت کنترل | قدرت ایستا | استحکام تنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>لکوموتیورانان | رؤسای قطار و مدیران محوطه راه‌آهن | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رانندگان مترو و تراموا | تعمیرکاران سیستم‌های علائم و سوزن‌های خطوط راه‌آهن | تعمیرکاران واگن‌های ریلی | اپراتورهای ماشین‌آلات ریل‌گذاری و نگهداری خطوط راه‌آهن | پلیس راه‌آهن و ناوگان حمل‌ونقل عمومی | بازرسان حمل‌ونقل | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری به‌استثنای هوانوردی | متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | متصدیان ترخیص و خدمات بار | اپراتورهای تراکتور و لیفتراک‌های صنعتی | اپراتورهای جرثقیل و تاورکرین | اپراتورها و متصدیان نقاله‌ها | سرپرستان رده‌اول سایر متصدیان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | کارگران جابه‌جایی دستی بار، کالا و کارهای عمومی | متصدیان پل‌های متحرک و آب‌بندها</t>
+          <t>لکوموتیورانان | رؤسای قطار و مدیران محوطه راه‌آهن | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رانندگان مترو و تراموا | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | تعمیرکار واگن قطار | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | پلیس ترانزیت و راه‌آهن | بازرسان ترابری و حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | متصدیان دیسپاچ و اعزام | کارگزاران حمل‌ونقل و بار | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای جرثقیل و تاورکرین | اپراتورها و متصدیان نوار نقاله | سرپرستان رده‌اول سایر کارکنان ترابری و حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | کارگران جابه‌جایی دستی بار، کالا و مصالح | متصدیان پل‌های متحرک و حوضچه‌های آرامش</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل‌ونقل | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | مکانیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید دور | دقت کنترل | درک شفاهی | حساسیت به مسئله | سرعت ادراک | ادراک عمق | توجه شنیداری | ثبات دست و بازو | هماهنگی چنداندامی | چابکی دستی | تشخیص رنگ بصری | توجه انتخابی | دید نزدیک | انعطاف‌پذیری بستار | حساسیت شنوایی | وضوح گفتار | تشخیص گفتار | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکتی | قدرت ایستا | زمان واکنش | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | استقامت بدنی | استحکام تنه | کنترل نرخ حرکتی | چابکی انگشتان | تقسیم توجه | جهت‌یابی فضایی | انعطاف‌پذیری دسته‌بندی | درک کتبی | جهت‌یابی منبع صوت | حساسیت به درخشش نور</t>
+          <t>بینایی دور | دقت کنترل | درک شفاهی | حساسیت به مسئله | سرعت ادراکی | درک عمق | توجه شنیداری | ثبات دست و بازو | هماهنگی چند عضو | مهارت دستی | تشخیص رنگ بصری | توجه انتخابی | بینایی نزدیک | انعطاف‌پذیری بستار | حساسیت شنوایی | وضوح گفتار | تشخیص گفتار | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | زمان عکس‌العمل | تجسم | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | استقامت | قدرت تنه | کنترل نرخ | مهارت انگشتان | تقسیم توجه | جهت‌گیری فضایی | انعطاف‌پذیری دسته‌بندی | درک کتبی | مکان‌یابی صدا | حساسیت به درخشندگی شدید</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | غواصان تجاری و صنعتی | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | کارگران صید و شکار | کارگران کمکی و ساده استخراج معدن | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و لیفتراک‌های صنعتی | تعمیرکاران و سرویس‌کاران ماشین‌آلات | مهندسان کشتی‌سازی و معماری دریایی | مکانیک‌ها و تعمیرکاران قایق‌های موتوری | قایقرانان قایق‌های موتوری | مهندسان بهره‌برداری و اپراتورهای سایر ماشین‌آلات ساختمانی | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | ریگرها و متصدیان دکل‌بندی و مهار بار | حفاران دکل‌های نفت و گاز | کارگران فنی و عمومی دکل‌های نفت و گاز | مهندسان فنی کشتی | متصدیان بارگیری مخزن‌دار ریلی، کامیونی و کشتی</t>
+          <t>مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | غواصان تجاری و صنعتی | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | صیادان، ماهیگیران و شکارچیان | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان دریایی و معماران کشتی | مکانیک و تکنسین شناورهای موتوری | قایقرانان قایق‌های موتوری | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | مهندسان فنی کشتی | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | امور حقوقی و دولتی | زبان انگلیسی | جغرافیا | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و تدریس</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | قانون و دولت | زبان انگلیسی | جغرافیا | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | جهت‌یابی فضایی | دید دور | وضوح گفتار | دید نزدیک | درک کتبی | دقت کنترل | ثبات دست و بازو | تشخیص گفتار | مرتب‌سازی اطلاعات | استدلال استقرایی | سرعت ادراک | انعطاف‌پذیری بستار | بیان کتبی | ادراک عمق | چابکی دستی | توجه انتخابی | تقسیم توجه | هماهنگی چنداندامی | کنترل نرخ حرکتی | زمان واکنش | حساسیت به درخشش نور | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | توجه شنیداری | تعادل کلی بدن | استحکام تنه | جهت‌گیری پاسخ | چابکی انگشتان | سرعت بستار | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکتی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | جهت‌گیری فضایی | بینایی دور | وضوح گفتار | بینایی نزدیک | درک کتبی | دقت کنترل | ثبات دست و بازو | تشخیص گفتار | ترتیب‌دهی اطلاعات | استدلال استقرایی | سرعت ادراکی | انعطاف‌پذیری بستار | بیان کتبی | درک عمق | مهارت دستی | توجه انتخابی | تقسیم توجه | هماهنگی چند عضو | کنترل نرخ | زمان عکس‌العمل | حساسیت به درخشندگی شدید | انعطاف‌پذیری دسته‌بندی | تجسم | توجه شنیداری | تعادل کلی بدن | قدرت تنه | جهت‌گیری پاسخ | مهارت انگشتان | سرعت بستار | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>سرپرستان جابه‌جایی بار هوایی | متخصصان عملیات فرودگاهی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | متصدیان پل‌های متحرک و آب‌بندها | غواصان تجاری و صنعتی | خلبانان تجاری | اپراتورهای لایروب | کارگران صید و شکار | اپراتورهای بالابر و وینچ | لکوموتیورانان | مهندسان کشتی‌سازی و معماری دریایی | قایقرانان قایق‌های موتوری | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | ریگرها و متصدیان دکل‌بندی و مهار بار | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | متصدیان بارگیری مخزن‌دار ریلی، کامیونی و کشتی | بازرسان حمل‌ونقل</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارشناسان عملیات فرودگاهی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | متصدیان پل‌های متحرک و حوضچه‌های آرامش | غواصان تجاری و صنعتی | خلبانان تجاری | اپراتورهای لایروب | صیادان، ماهیگیران و شکارچیان | اپراتورهای بالابر و وینچ | لکوموتیورانان | مهندسان دریایی و معماران کشتی | قایقرانان قایق‌های موتوری | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | شنیدن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | حمل‌ونقل | مکانیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | حمل و نقل | مکانیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دقت کنترل | جهت‌یابی فضایی | دید دور | حساسیت به مسئله | سرعت ادراک | ثبات دست و بازو | چابکی دستی | وضوح گفتار | توجه شنیداری | بیان شفاهی | هماهنگی چنداندامی | استدلال قیاسی | توجه انتخابی | جهت‌گیری پاسخ | زمان واکنش | دید نزدیک | ادراک عمق | تقسیم توجه | تشخیص گفتار | حساسیت به درخشش نور | کنترل نرخ حرکتی | چابکی انگشتان | انعطاف‌پذیری بستار | درک شفاهی | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت شنوایی | دید پیرامونی | تشخیص رنگ بصری | استحکام تنه | قدرت ایستا</t>
+          <t>دقت کنترل | جهت‌گیری فضایی | بینایی دور | حساسیت به مسئله | سرعت ادراکی | ثبات دست و بازو | مهارت دستی | وضوح گفتار | توجه شنیداری | بیان شفاهی | هماهنگی چند عضو | استدلال قیاسی | توجه انتخابی | جهت‌گیری پاسخ | زمان عکس‌العمل | بینایی نزدیک | درک عمق | تقسیم توجه | تشخیص گفتار | حساسیت به درخشندگی شدید | کنترل نرخ | مهارت انگشتان | انعطاف‌پذیری بستار | درک شفاهی | تجسم | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت شنوایی | بینایی محیطی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>سرپرستان جابه‌جایی بار هوایی | متصدیان پل‌های متحرک و آب‌بندها | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | خلبانان تجاری | اپراتورهای لایروب | کارگران صید و شکار | رانندگان تریلر و کامیون‌های سنگین | کارگران نگهداری و راهداری جاده‌ها | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و لیفتراک‌های صنعتی | لکوموتیورانان | مکانیک‌ها و تعمیرکاران قایق‌های موتوری | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | ریگرها و متصدیان دکل‌بندی و مهار بار | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | متصدیان بارگیری مخزن‌دار ریلی، کامیونی و کشتی | بازرسان حمل‌ونقل</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان پل‌های متحرک و حوضچه‌های آرامش | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | خلبانان تجاری | اپراتورهای لایروب | صیادان، ماهیگیران و شکارچیان | رانندگان خودروهای سنگین و کشنده‌ها | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | لکوموتیورانان | مکانیک و تکنسین شناورهای موتوری | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | سخن گفتن | یادگیری فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | فنی و مهندسی | ایمنی و امنیت عمومی | حمل‌ونقل | ریاضیات | رایانه و الکترونیک</t>
+          <t>مکانیک | زبان انگلیسی | مهندسی و فناوری | ایمنی و امنیت عمومی | حمل و نقل | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | دقت کنترل | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | مرتب‌سازی اطلاعات | توجه شنیداری | حساسیت شنوایی | زمان واکنش | هماهنگی چنداندامی | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | سرعت ادراک | ابتکار عمل | روانی ایده‌ها | جهت‌گیری پاسخ | تقسیم توجه | دید دور | انعطاف‌پذیری دامنه حرکتی | استحکام تنه | قدرت ایستا | کنترل نرخ حرکتی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | دقت کنترل | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | توجه شنیداری | حساسیت شنوایی | زمان عکس‌العمل | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | سرعت ادراکی | اصالت | روانی ایده‌ها | جهت‌گیری پاسخ | تقسیم توجه | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | کنترل نرخ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های مهندسی و عملیات هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکاران سازه، سطوح و سامانه‌های هوانوردی | تکنسین‌های اویونیک و الکترونیک هوانوردی | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌های نیروگاه‌های برق‌آبی | لکوموتیورانان | کارگران عمومی نگهداری و تعمیرات | مهندسان کشتی‌سازی و معماری دریایی | مکانیک‌های ماشین‌آلات سنگین متحرک به‌استثنای موتور | مکانیک‌ها و تعمیرکاران قایق‌های موتوری | مهندسان بهره‌برداری و اپراتورهای سایر ماشین‌آلات ساختمانی | اپراتورهای سامانه‌های پمپاژ نفت، پالایشگاه و سنجش مخازن | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای نیروگاه برق | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان تأسیسات و اپراتورهای دیگ بخار | بازرسان ناوگان، تجهیزات و سامانه‌های ترابری به‌استثنای هوانوردی | پمپ‌چی‌های سرچاهی نفت و گاز</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تکنسین‌های نیروگاه برقابی | لکوموتیورانان | کارگران عمومی تعمیرات و نگهداری تاسیسات | مهندسان دریایی و معماران کشتی | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
